--- a/MLOps/ROADMAP.xlsx
+++ b/MLOps/ROADMAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\MLOps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\github_loxford_pvt\MLOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC30D927-41B1-4FC9-9D9E-7CC63973E11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018702CA-B3E6-4755-B34C-46BCD3E97A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="2775" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="162">
   <si>
     <t>Phase</t>
   </si>
@@ -55,18 +55,6 @@
   </si>
   <si>
     <t>Explain ML lifecycle diagram</t>
-  </si>
-  <si>
-    <t>MLOps Overview</t>
-  </si>
-  <si>
-    <t>Roles in MLOps</t>
-  </si>
-  <si>
-    <t>Data Scientist vs ML Engineer vs DevOps</t>
-  </si>
-  <si>
-    <t>Real industry workflow</t>
   </si>
   <si>
     <t>Environment Setup</t>
@@ -633,8 +621,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G47" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="B1:G47" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G52" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B1:G52" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C1EF5561-1CEA-475F-8C66-9F535CF497F6}" name="Phase" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{B40C6DFB-4AB1-4F8D-9C13-F15D2B3BFA57}" name="Module" dataDxfId="4"/>
@@ -910,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -923,7 +911,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -941,7 +929,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1009,7 +997,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -1029,24 +1017,11 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1065,19 +1040,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -1086,22 +1061,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1109,19 +1084,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -1130,26 +1105,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1159,198 +1131,172 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1361,45 +1307,43 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>165</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G25" s="2"/>
     </row>
@@ -1413,71 +1357,60 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>24</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>91</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>27</v>
-      </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1486,94 +1419,79 @@
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1584,138 +1502,155 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>29</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>30</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>31</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>32</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="G43" s="2"/>
     </row>
@@ -1729,57 +1664,137 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G47" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G52" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MLOps/ROADMAP.xlsx
+++ b/MLOps/ROADMAP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\github_loxford_pvt\MLOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018702CA-B3E6-4755-B34C-46BCD3E97A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984A9A51-4B7A-420B-A0F0-FA01B14DA102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1305" windowWidth="28080" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="165">
   <si>
     <t>Phase</t>
   </si>
@@ -510,14 +510,23 @@
     <t>pdf+code+video done</t>
   </si>
   <si>
-    <t>pdf done</t>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>pdf + code done seperately</t>
+  </si>
+  <si>
+    <t>pdf + code done</t>
+  </si>
+  <si>
+    <t>PDF + Code done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,13 +542,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -554,12 +584,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -621,8 +657,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G52" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="B1:G52" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G51" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B1:G51" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C1EF5561-1CEA-475F-8C66-9F535CF497F6}" name="Phase" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{B40C6DFB-4AB1-4F8D-9C13-F15D2B3BFA57}" name="Module" dataDxfId="4"/>
@@ -898,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -955,7 +991,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -972,11 +1008,13 @@
       <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -993,11 +1031,13 @@
       <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -1014,7 +1054,9 @@
       <c r="F5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
@@ -1025,9 +1067,6 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1037,7 +1076,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
@@ -1058,7 +1097,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>22</v>
@@ -1081,7 +1120,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
@@ -1102,7 +1141,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>22</v>
@@ -1119,7 +1158,9 @@
       <c r="F11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="3" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
@@ -1130,9 +1171,6 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>11</v>
-      </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1142,7 +1180,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>39</v>
@@ -1163,7 +1201,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>39</v>
@@ -1184,7 +1222,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>39</v>
@@ -1205,7 +1243,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>52</v>
@@ -1242,7 +1280,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>57</v>
@@ -1265,7 +1303,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>57</v>
@@ -1287,136 +1325,129 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>19</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>20</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>21</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>23</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
@@ -1428,318 +1459,335 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G33" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>27</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>28</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>101</v>
-      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>158</v>
+        <v>92</v>
+      </c>
+      <c r="G37" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G38" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>31</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>32</v>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G41" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>8</v>
+      </c>
       <c r="B42" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>9</v>
+      </c>
       <c r="B45" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>9</v>
+      </c>
       <c r="B46" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>9</v>
+      </c>
       <c r="B47" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>142</v>
-      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -1747,16 +1795,16 @@
         <v>143</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G50" s="2"/>
     </row>
@@ -1765,36 +1813,18 @@
         <v>143</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G52" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MLOps/ROADMAP.xlsx
+++ b/MLOps/ROADMAP.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\github_loxford_pvt\MLOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984A9A51-4B7A-420B-A0F0-FA01B14DA102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00267843-5028-41D5-A81A-71D7C741CFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="1305" windowWidth="28080" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="168">
   <si>
     <t>Phase</t>
   </si>
@@ -510,6 +519,9 @@
     <t>pdf+code+video done</t>
   </si>
   <si>
+    <t>pdf done</t>
+  </si>
+  <si>
     <t>TODO</t>
   </si>
   <si>
@@ -520,13 +532,19 @@
   </si>
   <si>
     <t>PDF + Code done</t>
+  </si>
+  <si>
+    <t>code done</t>
+  </si>
+  <si>
+    <t>Smoke test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,14 +561,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -584,15 +594,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -657,8 +664,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G51" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="B1:G51" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G52" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B1:G52" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C1EF5561-1CEA-475F-8C66-9F535CF497F6}" name="Phase" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{B40C6DFB-4AB1-4F8D-9C13-F15D2B3BFA57}" name="Module" dataDxfId="4"/>
@@ -934,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -1009,7 +1016,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1032,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1055,7 +1062,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1137,7 +1144,9 @@
       <c r="F10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -1158,8 +1167,8 @@
       <c r="F11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>161</v>
+      <c r="G11" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1402,7 +1411,7 @@
         <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1445,8 +1454,8 @@
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>161</v>
+      <c r="G28" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1571,7 +1580,7 @@
         <v>92</v>
       </c>
       <c r="G37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1593,8 +1602,8 @@
       <c r="F38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>161</v>
+      <c r="G38" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1624,8 +1633,8 @@
       <c r="F40" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>161</v>
+      <c r="G40" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1647,8 +1656,8 @@
       <c r="F41" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>161</v>
+      <c r="G41" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1670,35 +1679,33 @@
       <c r="F42" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="A43">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>9</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1709,16 +1716,16 @@
         <v>126</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G45" s="2"/>
     </row>
@@ -1730,18 +1737,20 @@
         <v>126</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G46" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
@@ -1751,43 +1760,46 @@
         <v>126</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -1795,16 +1807,16 @@
         <v>143</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G50" s="2"/>
     </row>
@@ -1813,18 +1825,36 @@
         <v>143</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G51" s="2"/>
+      <c r="G52" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
